--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ22＋Ｂ6＋Ｃ27＋Ｄ57＝112。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ61＝117。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,14 +736,14 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-29</t>
         </is>
       </c>
     </row>
@@ -754,14 +754,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-22</t>
         </is>
       </c>
     </row>
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
@@ -793,18 +793,18 @@
         <v>0</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>+28</t>
+          <t>+29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>※ Ａ22件の内訳は、ほかの照会にまとめたもの18件と、当方の作業又は村の決定で決着したもの4件です。まとめたものの代表例は、高齢者世帯等除雪サービス事業に関する6件（Ｍ-49・55・56・57・58・65）を実施要綱のご提供と障がいのある方が属する世帯の利用実績の1件（Ｍ-56）にまとめたことです。Ｂは、当方が置いた見込みの想定を村に尋ねていたもの（Ｍ-90）、受領済みの原典で決まるもの（Ｍ-43・Ｍ-44・Ｍ-101・Ｍ-116）、当方の編集上の事項（Ｓ-25）です。Ｃは、公表資料で書ける部分を当方が書き、固有の事実だけを尋ねる形に絞ったものです。</t>
+          <t>※ Ａ23件の内訳は、ほかの照会にまとめたもの18件と、当方の作業又は村の決定で決着したもの5件です。まとめたものの代表例は、高齢者世帯等除雪サービス事業に関する6件（Ｍ-49・55・56・57・58・65）を実施要綱のご提供と障がいのある方が属する世帯の利用実績の1件（Ｍ-56）にまとめたことです。Ｂは、当方が置いた見込みの想定を村に尋ねていたもの（Ｍ-90）、受領済みの原典で決まるもの（Ｍ-43・Ｍ-44・Ｍ-101・Ｍ-116）、当方の編集上の事項（Ｓ-25）です。Ｃは、公表資料で書ける部分を当方が書き、固有の事実だけを尋ねる形に絞ったものです。</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項112件の区分と判断の理由</t>
+          <t>確認事項117件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -2975,9 +2975,9 @@
           <t>Ｍ-128</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査の対象者の内訳139名と配布数172の食い違い。村の抽出の記録</t>
+          <t>アンケート調査の対象者の内訳139名と配布数172の食い違い。令和8年10月21日版の集計表で内訳が「身体118名・精神34名・療育8名・入所等12名」（合計172名）に改められ、配布数と一致したため解消。増えた2件が自立支援医療受給者証の方と手帳等を持たない方であることも現物で確かめた</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-130</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>村内へのグループホームの設置の検討</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｍ-131</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
@@ -3087,49 +3087,45 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-12</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr"/>
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-19</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
@@ -3137,45 +3133,49 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-20</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr"/>
@@ -3183,7 +3183,7 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr"/>
@@ -3206,22 +3206,22 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｓ-23</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr"/>
@@ -3229,22 +3229,22 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-24</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr"/>
@@ -3252,22 +3252,22 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
@@ -3275,22 +3275,22 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
-        </is>
-      </c>
-      <c r="B107" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-26</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr"/>
@@ -3298,22 +3298,22 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
-        </is>
-      </c>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-27</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr"/>
@@ -3321,22 +3321,22 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｓ-28</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr"/>
@@ -3344,49 +3344,45 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr"/>
     </row>
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr"/>
@@ -3394,45 +3390,49 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-31</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr"/>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
-        </is>
-      </c>
-      <c r="B113" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>計画の体系（章立て）と成果品の構え</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr"/>
@@ -3509,25 +3509,140 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-36</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr"/>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-37</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="36" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-38</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr"/>
+      <c r="E119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-39</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr"/>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3544,7 +3659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3557,7 +3672,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの84件（村69件・他メンバー等15件）</t>
+          <t>ＣとＤの88件（村70件・他メンバー等18件）</t>
         </is>
       </c>
     </row>
@@ -5407,61 +5522,61 @@
     <row r="73" ht="34" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-128</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-129</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査の対象者の内訳と配布数</t>
+          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査の対象者の内訳139名と配布数172の食い違い。村の抽出の記録</t>
+          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
         </is>
       </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-129</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-130</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
+          <t>村内へのグループホームの設置の検討</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
+          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-131</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
@@ -5471,24 +5586,24 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
         </is>
       </c>
     </row>
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
@@ -5498,24 +5613,24 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
@@ -5525,24 +5640,24 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
@@ -5552,7 +5667,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5562,14 +5677,14 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
@@ -5579,7 +5694,7 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5589,14 +5704,14 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -5606,7 +5721,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5616,14 +5731,14 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -5633,24 +5748,24 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
@@ -5660,7 +5775,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -5670,68 +5785,68 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月16日（金）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
@@ -5741,7 +5856,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -5751,14 +5866,14 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
@@ -5768,24 +5883,24 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -5795,24 +5910,24 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -5822,7 +5937,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5832,34 +5947,142 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-37</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-38</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B90" s="15" t="inlineStr">
         <is>
           <t>Ｄ</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-39</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月30日（金）</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="34" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="34" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ61＝117。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ63＝119。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項117件の区分と判断の理由</t>
+          <t>確認事項119件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-132</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
@@ -3133,34 +3133,30 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-19</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr"/>
     </row>
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
+          <t>Ｓ-20</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -3170,35 +3166,39 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr"/>
@@ -3206,7 +3206,7 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr"/>
@@ -3252,22 +3252,22 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｓ-24</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
@@ -3275,22 +3275,22 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr"/>
@@ -3298,7 +3298,7 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
+          <t>Ｓ-26</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr"/>
@@ -3321,22 +3321,22 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
-        </is>
-      </c>
-      <c r="B109" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-27</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr"/>
@@ -3367,22 +3367,22 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr"/>
@@ -3390,34 +3390,30 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
+          <t>Ｓ-31</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -3427,35 +3423,39 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr"/>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B114" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>計画の体系（章立て）と成果品の構え</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr"/>
@@ -3486,7 +3486,7 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr"/>
@@ -3532,7 +3532,7 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr"/>
@@ -3578,7 +3578,7 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
@@ -3601,7 +3601,7 @@
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr"/>
@@ -3624,25 +3624,71 @@
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-41</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr"/>
+      <c r="E123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3659,7 +3705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3672,7 +3718,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの88件（村70件・他メンバー等18件）</t>
+          <t>ＣとＤの90件（村71件・他メンバー等19件）</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5649,7 @@
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-132</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
@@ -5613,7 +5659,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -5623,14 +5669,14 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
         </is>
       </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
@@ -5640,24 +5686,24 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
@@ -5667,24 +5713,24 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
@@ -5694,7 +5740,7 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5704,14 +5750,14 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -5721,7 +5767,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5731,14 +5777,14 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -5748,7 +5794,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5758,14 +5804,14 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
@@ -5775,24 +5821,24 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -5802,7 +5848,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5812,68 +5858,68 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月16日（金）</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
@@ -5883,7 +5929,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -5893,14 +5939,14 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -5910,24 +5956,24 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -5937,24 +5983,24 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
@@ -5964,7 +6010,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5974,14 +6020,14 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
@@ -5991,24 +6037,24 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
@@ -6018,24 +6064,24 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月30日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -6045,44 +6091,98 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
     </row>
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-41</t>
         </is>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B94" s="15" t="inlineStr">
         <is>
           <t>Ｄ</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ63＝119。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ77＝133。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項119件の区分と判断の理由</t>
+          <t>確認事項133件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -884,61 +884,53 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-40</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-13</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>工程の確認</t>
+          <t>施設入所支援4人の支給決定の内容</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>工程の確認。Ｍ-125 が同じ4つの日程（策定委員会・パブリックコメント・4町村広域・庁議と議会）を尋ねているため1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Ｍ-125</t>
-        </is>
-      </c>
+          <t>施設入所支援4人の支給決定の内容は村の支給決定の記録</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-41</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-14</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>医療的ケアサポート会議</t>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>医療的ケアサポート会議が基本指針の協議の場に当たるか。Ｍ-126（医療的ケア児等支援地域協議会と本村の協議の場）が同じ事項を扱うため1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-126</t>
-        </is>
-      </c>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数は村の台帳</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-42</t>
+          <t>Ｍ-15</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -948,12 +940,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値</t>
+          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
+          <t>令和9〜11年度に65歳に達する利用者の一覧は村の台帳</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
@@ -961,22 +953,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-43</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｍ-20</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>特定健康診査の受診率の基準値</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>特定健康診査の受診率の基準値。前回計画の本編を受領しており、第4次計画が掲げた基準値は原典で決まる。当方で解消すべき資料解釈上の疑問である</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者の一覧は村の台帳</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
@@ -984,22 +976,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-44</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｍ-21</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>計画の名称</t>
+          <t>令和9〜11年度の特別支援学校・特別支援学級の卒業予定者</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>計画の正式名称。前回計画の本編の表紙と村の策定委員会資料のいずれも「第４次北塩原村障がい者計画」であり、原典で決まる</t>
+          <t>卒業予定の方の一覧は教育委員会の記録。当方では把握できない</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
@@ -1007,22 +999,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-45</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-22</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数は村の把握</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
@@ -1030,22 +1022,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-46</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-24</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>移動支援の対象事業所</t>
+          <t>本村の住民が利用している村外の事業所の一覧</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
+          <t>村外の事業所の一覧は村の支給決定の記録。これがないと事業所への照会文を作れない</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -1053,22 +1045,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-47</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-25</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向は村が事業所から聞き取るもの</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
@@ -1076,7 +1068,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-48</t>
+          <t>Ｍ-26</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -1086,12 +1078,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>村単独事業の実績</t>
+          <t>医療的ケア者（成人）と重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
+          <t>医療的ケア者（成人）と重症心身障害の成人の方の人数は村の把握</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
@@ -1099,107 +1091,107 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-49</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-32</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の「等」の範囲</t>
+          <t>手帳を所持していないが対象疾病に該当する方の人数</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の「等」の範囲。除雪に関する6件（Ｍ-49・55・56・57・58・65）をＭ-56 に1件としてまとめる</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
+          <t>手帳を所持していないが対象疾病に該当する方の人数は村の支給決定の記録</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-50</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-37</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>高齢者福祉施策の「高齢者世帯等」に障がいのある方が入るか</t>
+          <t>給付費の財源構成（交付額と村の一般財源負担額）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>高齢者福祉施策13件の対象に障がいのある方が入るか。Ｍ-71 が除雪以外の8事業について同じことを尋ねているため1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Ｍ-71</t>
-        </is>
-      </c>
+          <t>給付費の交付額と村の一般財源負担額は村の決算</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-51</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-40</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の件数</t>
+          <t>工程の確認</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
+          <t>工程の確認。Ｍ-125 が同じ4つの日程（策定委員会・パブリックコメント・4町村広域・庁議と議会）を尋ねているため1件にまとめる</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-125</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-52</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-41</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
+          <t>医療的ケアサポート会議</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>医療的ケアサポート会議が基本指針の協議の場に当たるか。Ｍ-126（医療的ケア児等支援地域協議会と本村の協議の場）が同じ事項を扱うため1件にまとめる</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-126</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-53</t>
+          <t>Ｍ-42</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1209,12 +1201,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>就労の受け皿（職親委託等）</t>
+          <t>個別避難計画の令和7年度の現在値</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
+          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -1222,22 +1214,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-54</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-43</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の5機能の実績</t>
+          <t>特定健康診査の受診率の基準値</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
+          <t>特定健康診査の受診率の基準値。前回計画の本編を受領しており、第4次計画が掲げた基準値は原典で決まる。当方で解消すべき資料解釈上の疑問である</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
@@ -1245,34 +1237,30 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-55</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-44</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の利用実績</t>
+          <t>計画の名称</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>除雪サービスの利用実績。Ｍ-56 にまとめる</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
+          <t>計画の正式名称。前回計画の本編の表紙と村の策定委員会資料のいずれも「第４次北塩原村障がい者計画」であり、原典で決まる</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-56</t>
+          <t>Ｍ-45</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1282,12 +1270,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
+          <t>北塩原村地域公共交通計画</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
+          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -1295,111 +1283,103 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-57</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-46</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>冬季の除雪の供給の制約</t>
+          <t>移動支援の対象事業所</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>冬季の除雪の供給の制約。Ｍ-56 にまとめる</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
+          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-58</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-47</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>除雪が困難な世帯を既存事業へつなぐ運用</t>
+          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>除雪が困難な世帯を既存事業へつなぐ運用。Ｍ-56 にまとめる</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
+          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-59</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-48</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>手話に関する情報発信の実績</t>
+          <t>村単独事業の実績</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>手話に関する情報発信の実績。Ｍ-60 と合わせて手話言語条例に基づく取組の実績1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-60</t>
-        </is>
-      </c>
+          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-60</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-49</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>手話出前講座の実績</t>
+          <t>高齢者世帯等除雪サービス事業の「等」の範囲</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
+          <t>高齢者世帯等除雪サービス事業の「等」の範囲。除雪に関する6件（Ｍ-49・55・56・57・58・65）をＭ-56 に1件としてまとめる</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-61</t>
+          <t>Ｍ-50</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1409,24 +1389,24 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>電話お願い手帳</t>
+          <t>高齢者福祉施策の「高齢者世帯等」に障がいのある方が入るか</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>電話お願い手帳。Ｍ-62（本人に代わって伝えるための道具の配布実績）にまとめる</t>
+          <t>高齢者福祉施策13件の対象に障がいのある方が入るか。Ｍ-71 が除雪以外の8事業について同じことを尋ねているため1件にまとめる</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-62</t>
+          <t>Ｍ-71</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-62</t>
+          <t>Ｍ-51</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -1436,12 +1416,12 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マークの配布実績</t>
+          <t>権利擁護・成年後見の件数</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
+          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
@@ -1449,7 +1429,7 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-63</t>
+          <t>Ｍ-52</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -1459,12 +1439,12 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績</t>
+          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
+          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
@@ -1472,61 +1452,53 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-64</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-53</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>人工透析患者通院交通費助成の実績</t>
+          <t>就労の受け皿（職親委託等）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>人工透析患者通院交通費助成の実績。Ｍ-48（村単独事業の実績）に含める</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Ｍ-48</t>
-        </is>
-      </c>
+          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-65</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-54</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>除雪サービスの障がい者世帯の利用実績</t>
+          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>除雪サービスの障がい者世帯の利用実績。Ｍ-56 にまとめる</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
+          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-66</t>
+          <t>Ｍ-55</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1536,135 +1508,143 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>パラスポーツへの村民の参加</t>
+          <t>高齢者世帯等除雪サービス事業の利用実績</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>パラスポーツへの村民の参加。Ｍ-111（生涯学習・スポーツ・文化の参加実績）に含める</t>
+          <t>除雪サービスの利用実績。Ｍ-56 にまとめる</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-111</t>
+          <t>Ｍ-56</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-67</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>北塩原村障がい者活躍推進計画</t>
+          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>北塩原村障がい者活躍推進計画。Ｍ-122 が第2期計画の内容を尋ねているため1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-122</t>
-        </is>
-      </c>
+          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-68</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-57</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>物品等の調達方針と実績</t>
+          <t>冬季の除雪の供給の制約</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr"/>
+          <t>冬季の除雪の供給の制約。Ｍ-56 にまとめる</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-69</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-58</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>印刷の色</t>
+          <t>除雪が困難な世帯を既存事業へつなぐ運用</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
+          <t>除雪が困難な世帯を既存事業へつなぐ運用。Ｍ-56 にまとめる</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-70</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-59</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>こども計画の名称と根拠法令</t>
+          <t>手話に関する情報発信の実績</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
+          <t>手話に関する情報発信の実績。Ｍ-60 と合わせて手話言語条例に基づく取組の実績1件にまとめる</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-60</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-71</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-60</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の障がい者の利用</t>
+          <t>手話出前講座の実績</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
+          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
@@ -1672,57 +1652,57 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-72</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-61</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>高齢者向けの共同生活の住まい</t>
+          <t>電話お願い手帳</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
+          <t>電話お願い手帳。Ｍ-62（本人に代わって伝えるための道具の配布実績）にまとめる</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-62</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-73</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-62</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>おもいやり駐車場とヘルプマーク等の配布実績</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>おもいやり駐車場とヘルプマーク等の配布実績。Ｍ-62 にまとめる</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-62</t>
-        </is>
-      </c>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-74</t>
+          <t>Ｍ-63</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -1732,12 +1712,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の障がい児の受入れ</t>
+          <t>「つなぐ窓口」の相談実績</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
+          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
@@ -1745,99 +1725,115 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-75</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-64</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>一般の子育て施策における障がい児の受入れ</t>
+          <t>人工透析患者通院交通費助成の実績</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
+          <t>人工透析患者通院交通費助成の実績。Ｍ-48（村単独事業の実績）に含める</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-48</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-76</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-65</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>早期発見から支援への接続件数</t>
+          <t>除雪サービスの障がい者世帯の利用実績</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr"/>
+          <t>除雪サービスの障がい者世帯の利用実績。Ｍ-56 にまとめる</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-77</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-66</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数</t>
+          <t>パラスポーツへの村民の参加</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr"/>
+          <t>パラスポーツへの村民の参加。Ｍ-111（生涯学習・スポーツ・文化の参加実績）に含める</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-111</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-78</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-67</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」の配布と活用</t>
+          <t>北塩原村障がい者活躍推進計画</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
+          <t>北塩原村障がい者活躍推進計画。Ｍ-122 が第2期計画の内容を尋ねているため1件にまとめる</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-122</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-79</t>
+          <t>Ｍ-68</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -1847,12 +1843,12 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>人権相談の実績と受付の経路</t>
+          <t>物品等の調達方針と令和6年度以降の実績</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
+          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr"/>
@@ -1860,22 +1856,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-80</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-69</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>矯正施設を退所した方への支援の実績</t>
+          <t>印刷の色</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
+          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr"/>
@@ -1883,22 +1879,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-81</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-70</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
+          <t>こども計画の名称と根拠法令</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
+          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
@@ -1906,22 +1902,22 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-82</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-71</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>救急電話相談の代替手段</t>
+          <t>高齢者福祉事業の障がい者の利用</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
+          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr"/>
@@ -1929,22 +1925,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-83</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-72</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達</t>
+          <t>高齢者向けの共同生活の住まい</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
+          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
@@ -1952,30 +1948,34 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-84</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-73</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>AEDの設置状況と救命講習</t>
+          <t>おもいやり駐車場とヘルプマーク等の配布実績</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
+          <t>おもいやり駐車場とヘルプマーク等の配布実績。Ｍ-62 にまとめる</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-62</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-85</t>
+          <t>Ｍ-74</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績</t>
+          <t>子育て短期支援事業の障がい児の受入れ</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
+          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
@@ -1998,34 +1998,30 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-86</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-75</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>地域生活支援拠点による代替調整の実績</t>
+          <t>一般の子育て施策における障がい児の受入れ</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>地域生活支援拠点による代替調整の実績。照会文に「Ｍ-54と同じ便で尋ねる」と書いており、Ｍ-54 にまとめる</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Ｍ-54</t>
-        </is>
-      </c>
+          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-87</t>
+          <t>Ｍ-76</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -2035,12 +2031,12 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>訪問系サービスの対象となりうる方の個別の状況</t>
+          <t>早期発見から支援への接続件数</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
+          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr"/>
@@ -2048,22 +2044,22 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-88</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-77</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>訪問系サービスの有資格者の確保</t>
+          <t>特別児童扶養手当の受給児童数</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
+          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
@@ -2071,22 +2067,22 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-89</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-78</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差</t>
+          <t>「わたしの思いノート」の配布と活用</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
+          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
@@ -2094,22 +2090,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-90</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｍ-79</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>短期入所の利用の場面と自立訓練（生活訓練）の期間</t>
+          <t>人権相談の実績と受付の経路</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>短期入所1人・5人日／月と自立訓練（生活訓練）1人・12人日は当方が第1次概算で置いた見込みである。その想定を村に尋ねるのは当方の作業の転嫁に当たる。当方で利用の場面と回数の案を整理し、第2次算定（Ｍ-18・Ｍ-19の受領後）で確定する</t>
+          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
@@ -2117,22 +2113,22 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-91</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-80</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
+          <t>矯正施設を退所した方への支援の実績</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
+          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
@@ -2140,22 +2136,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-92</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-81</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>就労系サービスの個人の経路</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
@@ -2163,22 +2159,22 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-93</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-82</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
+          <t>救急電話相談の代替手段</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
+          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
@@ -2186,7 +2182,7 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-94</t>
+          <t>Ｍ-83</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -2196,12 +2192,12 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
+          <t>個別避難計画の対象者への情報伝達</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
+          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
@@ -2209,22 +2205,22 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-95</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-84</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の指標の最新値</t>
+          <t>AEDの設置状況と救命講習</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
+          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
@@ -2232,7 +2228,7 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-96</t>
+          <t>Ｍ-85</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -2242,12 +2238,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況</t>
+          <t>積雪・通行規制によるサービスの中断実績</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
+          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr"/>
@@ -2255,30 +2251,34 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-97</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-86</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
+          <t>地域生活支援拠点による代替調整の実績</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
+          <t>地域生活支援拠点による代替調整の実績。照会文に「Ｍ-54と同じ便で尋ねる」と書いており、Ｍ-54 にまとめる</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-54</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-98</t>
+          <t>Ｍ-87</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
+          <t>訪問系サービスの対象となりうる方の個別の状況</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
+          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr"/>
@@ -2301,22 +2301,22 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-99</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-88</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会</t>
+          <t>訪問系サービスの有資格者の確保</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
+          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-100</t>
+          <t>Ｍ-89</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方</t>
+          <t>居宅介護の支給決定量と実利用量の差</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
+          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-101</t>
+          <t>Ｍ-90</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>会津権利擁護・成年後見センターの構成市町村</t>
+          <t>短期入所の利用の場面と自立訓練（生活訓練）の期間</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>会津権利擁護・成年後見センターの構成市町村。第7期福島県障がい福祉計画（206頁・受領済み）の第9 圏域計画で確かめられる</t>
+          <t>短期入所1人・5人日／月と自立訓練（生活訓練）1人・12人日は当方が第1次概算で置いた見込みである。その想定を村に尋ねるのは当方の作業の転嫁に当たる。当方で利用の場面と回数の案を整理し、第2次算定（Ｍ-18・Ｍ-19の受領後）で確定する</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr"/>
@@ -2370,22 +2370,22 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-102</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-91</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>児童発達支援センターの４つの中核機能の接続先</t>
+          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
+          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr"/>
@@ -2393,22 +2393,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-103</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-92</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無</t>
+          <t>就労系サービスの個人の経路</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
+          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
@@ -2416,22 +2416,22 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-104</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-93</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
+          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
+          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr"/>
@@ -2439,22 +2439,22 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-105</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-94</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr"/>
@@ -2462,22 +2462,22 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-106</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-95</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
+          <t>第4次障がい者計画の指標の最新値</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
+          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr"/>
@@ -2485,22 +2485,22 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-107</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-96</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
+          <t>障がいのある方の特定健康診査の受診状況</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
+          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-108</t>
+          <t>Ｍ-97</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
+          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
+          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-109</t>
+          <t>Ｍ-98</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
+          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
+          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-110</t>
+          <t>Ｍ-99</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無</t>
+          <t>福島県（会津保健福祉事務所）への照会</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
+          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr"/>
@@ -2577,22 +2577,22 @@
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-111</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-100</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
+          <t>医療的ケア児等コーディネーターとして数えている方</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
+          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr"/>
@@ -2600,22 +2600,22 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-112</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-101</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>成果品の印刷・製本の所要日数と発注の形</t>
+          <t>会津権利擁護・成年後見センターの構成市町村</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
+          <t>会津権利擁護・成年後見センターの構成市町村。第7期福島県障がい福祉計画（206頁・受領済み）の第9 圏域計画で確かめられる</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr"/>
@@ -2623,22 +2623,22 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-113</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-102</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
+          <t>児童発達支援センターの４つの中核機能の接続先</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
+          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-114</t>
+          <t>Ｍ-103</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-115</t>
+          <t>Ｍ-104</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
+          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
+          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr"/>
@@ -2692,22 +2692,22 @@
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-116</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｍ-105</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の見直しに伴う村の事務</t>
+          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>民法等の一部を改正する法律（令和8年法律第45号）の概要を受領済み。村の事務への影響は条文から整理できる。施行日が未確定である点はＳ-35（追加告示）と合わせて扱う</t>
+          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr"/>
@@ -2715,22 +2715,22 @@
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-117</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-106</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
+          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
+          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-118</t>
+          <t>Ｍ-107</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
+          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-119</t>
+          <t>Ｍ-108</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
+          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
+          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-120</t>
+          <t>Ｍ-109</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>医療的ケアの担い手と非常用電源</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr"/>
@@ -2807,22 +2807,22 @@
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-121</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-110</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
+          <t>障害者基本法第36条の合議制の機関の有無</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
+          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-122</t>
+          <t>Ｍ-111</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
+          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
+          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr"/>
@@ -2853,34 +2853,30 @@
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-123</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-112</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>策定の工程の引き直しと、パブリックコメントの期間の根拠</t>
+          <t>成果品の印刷・製本の所要日数と発注の形</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>策定の工程の引き直しとパブリックコメントの期間の根拠。Ｍ-125 が同じ事項をより詳しく尋ねているため1件にまとめる</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>Ｍ-125</t>
-        </is>
-      </c>
+          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr"/>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-124</t>
+          <t>Ｍ-113</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -2890,12 +2886,12 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
@@ -2903,7 +2899,7 @@
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-125</t>
+          <t>Ｍ-114</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
@@ -2913,12 +2909,12 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr"/>
@@ -2926,22 +2922,22 @@
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-126</t>
-        </is>
-      </c>
-      <c r="B92" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-115</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
+          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
+          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr"/>
@@ -2949,22 +2945,22 @@
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-127</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-116</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続</t>
+          <t>成年後見制度の見直しに伴う村の事務</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
+          <t>民法等の一部を改正する法律（令和8年法律第45号）の概要を受領済み。村の事務への影響は条文から整理できる。施行日が未確定である点はＳ-35（追加告示）と合わせて扱う</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr"/>
@@ -2972,22 +2968,22 @@
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-128</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-117</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査の対象者の内訳と配布数</t>
+          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査の対象者の内訳139名と配布数172の食い違い。令和8年10月21日版の集計表で内訳が「身体118名・精神34名・療育8名・入所等12名」（合計172名）に改められ、配布数と一致したため解消。増えた2件が自立支援医療受給者証の方と手帳等を持たない方であることも現物で確かめた</t>
+          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr"/>
@@ -2995,7 +2991,7 @@
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-129</t>
+          <t>Ｍ-118</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -3005,12 +3001,12 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
+          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
+          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr"/>
@@ -3018,7 +3014,7 @@
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-130</t>
+          <t>Ｍ-119</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -3028,12 +3024,12 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置の検討</t>
+          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
+          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr"/>
@@ -3041,7 +3037,7 @@
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-131</t>
+          <t>Ｍ-120</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
@@ -3051,12 +3047,12 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
+          <t>医療的ケアの担い手と非常用電源</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
+          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr"/>
@@ -3064,22 +3060,22 @@
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-132</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-121</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
+          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
+          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
@@ -3087,22 +3083,22 @@
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-122</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr"/>
@@ -3110,30 +3106,34 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-123</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>策定の工程の引き直しと、パブリックコメントの期間の根拠</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr"/>
+          <t>策定の工程の引き直しとパブリックコメントの期間の根拠。Ｍ-125 が同じ事項をより詳しく尋ねているため1件にまとめる</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-125</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｍ-124</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr"/>
@@ -3156,49 +3156,45 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-125</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-126</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
+          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr"/>
@@ -3206,7 +3202,7 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｍ-127</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -3216,12 +3212,12 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>障がい児支援の人材と事業所の継続</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr"/>
@@ -3229,22 +3225,22 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
-        </is>
-      </c>
-      <c r="B105" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-128</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>アンケート調査の対象者の内訳と配布数</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>アンケート調査の対象者の内訳139名と配布数172の食い違い。令和8年10月21日版の集計表で内訳が「身体118名・精神34名・療育8名・入所等12名」（合計172名）に改められ、配布数と一致したため解消。増えた2件が自立支援医療受給者証の方と手帳等を持たない方であることも現物で確かめた</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr"/>
@@ -3252,22 +3248,22 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｍ-129</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
@@ -3275,22 +3271,22 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｍ-130</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>村内へのグループホームの設置の検討</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr"/>
@@ -3298,22 +3294,22 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-131</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr"/>
@@ -3321,22 +3317,22 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-132</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr"/>
@@ -3344,7 +3340,7 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｍ-133</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -3354,12 +3350,12 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>北塩原村障がい者自立支援協議会の委員名簿（令和8年度時点）</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>自立支援協議会の令和8年度時点の委員は村の委嘱の記録。資料編に実名が載るため当方の推測では置けない</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr"/>
@@ -3367,7 +3363,7 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｍ-134</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
@@ -3377,12 +3373,12 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>障がい者相談支援事業の2カ所のうち村の担当課</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>相談支援事業を担う課の名称と改編の経緯は村の内部。村ホームページでは保健福祉課が相談の窓口であることまでしか分からない</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr"/>
@@ -3390,22 +3386,22 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｍ-135</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>北塩原村の地域福祉計画の有無と策定の状況</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>地域福祉計画の有無と策定の予定は村の判断。村ホームページは当方の環境から閲覧できない</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr"/>
@@ -3413,49 +3409,45 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-11</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr"/>
     </row>
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-12</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
@@ -3463,7 +3455,7 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -3473,12 +3465,12 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr"/>
@@ -3486,45 +3478,49 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
-        </is>
-      </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-20</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr"/>
@@ -3532,7 +3528,7 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -3542,12 +3538,12 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
@@ -3555,7 +3551,7 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -3565,12 +3561,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr"/>
@@ -3578,7 +3574,7 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -3588,12 +3584,12 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
@@ -3601,22 +3597,22 @@
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
-        </is>
-      </c>
-      <c r="B121" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr"/>
@@ -3624,22 +3620,22 @@
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
-        </is>
-      </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-26</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
@@ -3647,22 +3643,22 @@
     <row r="123" ht="36" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-27</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr"/>
@@ -3670,25 +3666,351 @@
     <row r="124" ht="36" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>Ｓ-28</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr"/>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-31</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>計画の体系（章立て）と成果品の構え</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-33</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>第3章の章題の変更と目次の更新</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr"/>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-34</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の追加告示の入手と最終照合</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr"/>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-36</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-37</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr"/>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-38</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-39</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr"/>
+    </row>
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr"/>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-42</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr"/>
+      <c r="E138" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3705,7 +4027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3718,7 +4040,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの90件（村71件・他メンバー等19件）</t>
+          <t>ＣとＤの104件（村85件・他メンバー等19件）</t>
         </is>
       </c>
     </row>
@@ -3759,7 +4081,7 @@
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-42</t>
+          <t>Ｍ-13</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -3769,105 +4091,105 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値</t>
+          <t>施設入所支援4人の支給決定の内容</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
+          <t>施設入所支援4人の支給決定の内容は村の支給決定の記録</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-45</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-14</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画</t>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-46</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-15</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>移動支援の対象事業所</t>
+          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
+          <t>令和9〜11年度に65歳に達する利用者の一覧は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-47</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-20</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者の一覧は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-48</t>
+          <t>Ｍ-21</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -3877,24 +4199,24 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>村単独事業の実績</t>
+          <t>令和9〜11年度の特別支援学校・特別支援学級の卒業予定者</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
+          <t>卒業予定の方の一覧は教育委員会の記録。当方では把握できない</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-51</t>
+          <t>Ｍ-22</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -3904,24 +4226,24 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の件数</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数は村の把握</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-52</t>
+          <t>Ｍ-24</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -3931,24 +4253,24 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
+          <t>本村の住民が利用している村外の事業所の一覧</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
+          <t>村外の事業所の一覧は村の支給決定の記録。これがないと事業所への照会文を作れない</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-53</t>
+          <t>Ｍ-25</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -3958,24 +4280,24 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>就労の受け皿（職親委託等）</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向は村が事業所から聞き取るもの</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-54</t>
+          <t>Ｍ-26</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -3985,78 +4307,78 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の5機能の実績</t>
+          <t>医療的ケア者（成人）と重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
+          <t>医療的ケア者（成人）と重症心身障害の成人の方の人数は村の把握</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-32</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
+          <t>手帳を所持していないが対象疾病に該当する方の人数</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
+          <t>手帳を所持していないが対象疾病に該当する方の人数は村の支給決定の記録</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-60</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-37</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>手話出前講座の実績</t>
+          <t>給付費の財源構成（交付額と村の一般財源負担額）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
+          <t>給付費の交付額と村の一般財源負担額は村の決算</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-62</t>
+          <t>Ｍ-42</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -4066,51 +4388,51 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マークの配布実績</t>
+          <t>個別避難計画の令和7年度の現在値</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
+          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-63</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-45</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績</t>
+          <t>北塩原村地域公共交通計画</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
+          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-68</t>
+          <t>Ｍ-46</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -4120,7 +4442,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>物品等の調達方針と実績</t>
+          <t>移動支援の対象事業所</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -4130,24 +4452,24 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
+          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-69</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-47</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>印刷の色</t>
+          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -4157,24 +4479,24 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
+          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-70</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-48</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>こども計画の名称と根拠法令</t>
+          <t>村単独事業の実績</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -4184,14 +4506,14 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
+          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-71</t>
+          <t>Ｍ-51</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
@@ -4201,7 +4523,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の障がい者の利用</t>
+          <t>権利擁護・成年後見の件数</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -4211,24 +4533,24 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
+          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-72</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-52</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>高齢者向けの共同生活の住まい</t>
+          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -4238,14 +4560,14 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
+          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-74</t>
+          <t>Ｍ-53</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -4255,24 +4577,24 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の障がい児の受入れ</t>
+          <t>就労の受け皿（職親委託等）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
+          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-75</t>
+          <t>Ｍ-54</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
@@ -4282,34 +4604,34 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>一般の子育て施策における障がい児の受入れ</t>
+          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
+          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-76</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>早期発見から支援への接続件数</t>
+          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -4319,95 +4641,95 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
+          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-77</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-60</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数</t>
+          <t>手話出前講座の実績</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
+          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-78</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-62</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」の配布と活用</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-79</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-63</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>人権相談の実績と受付の経路</t>
+          <t>「つなぐ窓口」の相談実績</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
+          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-80</t>
+          <t>Ｍ-68</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -4417,7 +4739,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>矯正施設を退所した方への支援の実績</t>
+          <t>物品等の調達方針と令和6年度以降の実績</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -4427,14 +4749,14 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
+          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-81</t>
+          <t>Ｍ-69</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
@@ -4444,7 +4766,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
+          <t>印刷の色</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -4454,14 +4776,14 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
+          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
         </is>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-82</t>
+          <t>Ｍ-70</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
@@ -4471,7 +4793,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>救急電話相談の代替手段</t>
+          <t>こども計画の名称と根拠法令</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -4481,14 +4803,14 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
+          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-83</t>
+          <t>Ｍ-71</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
@@ -4498,7 +4820,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達</t>
+          <t>高齢者福祉事業の障がい者の利用</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -4508,14 +4830,14 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
+          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-84</t>
+          <t>Ｍ-72</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
@@ -4525,7 +4847,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>AEDの設置状況と救命講習</t>
+          <t>高齢者向けの共同生活の住まい</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -4535,14 +4857,14 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
+          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-85</t>
+          <t>Ｍ-74</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
@@ -4552,7 +4874,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績</t>
+          <t>子育て短期支援事業の障がい児の受入れ</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4562,14 +4884,14 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
+          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
         </is>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-87</t>
+          <t>Ｍ-75</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -4579,7 +4901,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>訪問系サービスの対象となりうる方の個別の状況</t>
+          <t>一般の子育て施策における障がい児の受入れ</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -4589,24 +4911,24 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
+          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
         </is>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-88</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-76</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>訪問系サービスの有資格者の確保</t>
+          <t>早期発見から支援への接続件数</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4616,14 +4938,14 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
+          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
         </is>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-89</t>
+          <t>Ｍ-77</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
@@ -4633,7 +4955,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差</t>
+          <t>特別児童扶養手当の受給児童数</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -4643,24 +4965,24 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
+          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-91</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-78</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
+          <t>「わたしの思いノート」の配布と活用</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4670,14 +4992,14 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
+          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
         </is>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-92</t>
+          <t>Ｍ-79</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
@@ -4687,7 +5009,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>就労系サービスの個人の経路</t>
+          <t>人権相談の実績と受付の経路</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -4697,24 +5019,24 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
+          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-93</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-80</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
+          <t>矯正施設を退所した方への支援の実績</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -4724,14 +5046,14 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
+          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-94</t>
+          <t>Ｍ-81</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
@@ -4741,7 +5063,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -4751,24 +5073,24 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-95</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-82</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の指標の最新値</t>
+          <t>救急電話相談の代替手段</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -4778,14 +5100,14 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
+          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-96</t>
+          <t>Ｍ-83</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
@@ -4795,7 +5117,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況</t>
+          <t>個別避難計画の対象者への情報伝達</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4805,41 +5127,41 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
+          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-97</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-84</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
+          <t>AEDの設置状況と救命講習</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
+          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-98</t>
+          <t>Ｍ-85</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
@@ -4849,24 +5171,24 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
+          <t>積雪・通行規制によるサービスの中断実績</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
+          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-99</t>
+          <t>Ｍ-87</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
@@ -4876,78 +5198,78 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会</t>
+          <t>訪問系サービスの対象となりうる方の個別の状況</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
+          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-100</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-88</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方</t>
+          <t>訪問系サービスの有資格者の確保</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
+          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-102</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-89</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>児童発達支援センターの４つの中核機能の接続先</t>
+          <t>居宅介護の支給決定量と実利用量の差</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
+          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-103</t>
+          <t>Ｍ-91</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
@@ -4957,24 +5279,24 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無</t>
+          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
+          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-104</t>
+          <t>Ｍ-92</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
@@ -4984,105 +5306,105 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
+          <t>就労系サービスの個人の経路</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
+          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-105</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-93</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
+          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
+          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
         </is>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-106</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-94</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-107</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-95</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
+          <t>第4次障がい者計画の指標の最新値</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
+          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-108</t>
+          <t>Ｍ-96</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
@@ -5092,24 +5414,24 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
+          <t>障がいのある方の特定健康診査の受診状況</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
+          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-109</t>
+          <t>Ｍ-97</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
@@ -5119,24 +5441,24 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
+          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
+          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-110</t>
+          <t>Ｍ-98</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
@@ -5146,51 +5468,51 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無</t>
+          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
+          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-111</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-99</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
+          <t>福島県（会津保健福祉事務所）への照会</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
+          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
         </is>
       </c>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-112</t>
+          <t>Ｍ-100</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr">
@@ -5200,51 +5522,51 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>成果品の印刷・製本の所要日数と発注の形</t>
+          <t>医療的ケア児等コーディネーターとして数えている方</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
+          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
         </is>
       </c>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-113</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-102</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
+          <t>児童発達支援センターの４つの中核機能の接続先</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
+          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
         </is>
       </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-114</t>
+          <t>Ｍ-103</t>
         </is>
       </c>
       <c r="B61" s="15" t="inlineStr">
@@ -5254,7 +5576,7 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -5264,14 +5586,14 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-115</t>
+          <t>Ｍ-104</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -5281,51 +5603,51 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
+          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
+          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
         </is>
       </c>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-117</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-105</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
+          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
+          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
         </is>
       </c>
     </row>
     <row r="64" ht="34" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-118</t>
+          <t>Ｍ-106</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -5335,51 +5657,51 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
+          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
+          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-119</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-107</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
+          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
         </is>
       </c>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-120</t>
+          <t>Ｍ-108</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
@@ -5389,105 +5711,105 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>医療的ケアの担い手と非常用電源</t>
+          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
+          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
         </is>
       </c>
     </row>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-121</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-109</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
         </is>
       </c>
     </row>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-122</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-110</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
+          <t>障害者基本法第36条の合議制の機関の有無</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
+          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
     </row>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-124</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-111</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
+          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
+          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
         </is>
       </c>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-125</t>
+          <t>Ｍ-112</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
@@ -5497,24 +5819,24 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
+          <t>成果品の印刷・製本の所要日数と発注の形</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
+          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
         </is>
       </c>
     </row>
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-126</t>
+          <t>Ｍ-113</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
@@ -5524,24 +5846,24 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
         </is>
       </c>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-127</t>
+          <t>Ｍ-114</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
@@ -5551,7 +5873,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -5561,14 +5883,14 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
         </is>
       </c>
     </row>
     <row r="73" ht="34" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-129</t>
+          <t>Ｍ-115</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
@@ -5578,24 +5900,24 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
+          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
+          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
         </is>
       </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-130</t>
+          <t>Ｍ-117</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
@@ -5605,51 +5927,51 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置の検討</t>
+          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
+          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-131</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-118</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
+          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
+          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
         </is>
       </c>
     </row>
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-132</t>
+          <t>Ｍ-119</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
@@ -5659,24 +5981,24 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
+          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
+          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
         </is>
       </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-120</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
@@ -5686,78 +6008,78 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>医療的ケアの担い手と非常用電源</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
         </is>
       </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
-        </is>
-      </c>
-      <c r="B78" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-121</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
-        </is>
-      </c>
-      <c r="B79" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-122</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｍ-124</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -5767,24 +6089,24 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｍ-125</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -5794,24 +6116,24 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｍ-126</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
@@ -5821,24 +6143,24 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｍ-127</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -5848,78 +6170,78 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>障がい児支援の人材と事業所の継続</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
         </is>
       </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
-        </is>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-129</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
         </is>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-130</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>村内へのグループホームの設置の検討</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
         </is>
       </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
+          <t>Ｍ-131</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
@@ -5929,24 +6251,24 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
         </is>
       </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｍ-132</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -5956,24 +6278,24 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｍ-133</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -5983,7 +6305,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>北塩原村障がい者自立支援協議会の委員名簿（令和8年度時点）</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5993,14 +6315,14 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>自立支援協議会の令和8年度時点の委員は村の委嘱の記録。資料編に実名が載るため当方の推測では置けない</t>
         </is>
       </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｍ-134</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
@@ -6010,24 +6332,24 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>障がい者相談支援事業の2カ所のうち村の担当課</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>相談支援事業を担う課の名称と改編の経緯は村の内部。村ホームページでは保健福祉課が相談の窓口であることまでしか分からない</t>
         </is>
       </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｍ-135</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
@@ -6037,24 +6359,24 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>北塩原村の地域福祉計画の有無と策定の状況</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>地域福祉計画の有無と策定の予定は村の判断。村ホームページは当方の環境から閲覧できない</t>
         </is>
       </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
@@ -6064,7 +6386,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -6074,14 +6396,14 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -6091,24 +6413,24 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
@@ -6118,24 +6440,24 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -6145,42 +6467,420 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-23</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>計画の位置づけ図の重複</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="34" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-24</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>画像内の表題の扱い</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="34" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-28</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="34" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月16日（金）</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="34" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-33</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>第3章の章題の変更と目次の更新</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-34</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="34" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>基本指針の追加告示の入手と最終照合</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="34" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-36</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="34" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-37</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月16日</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-38</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="34" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-39</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>令和８年11月14日（金）</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="34" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-42</t>
         </is>
       </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
         </is>
@@ -6274,7 +6974,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の5機能の実績</t>
+          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -6334,7 +7034,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マークの配布実績</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">

--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ23＋Ｂ6＋Ｃ27＋Ｄ77＝133。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ24＋Ｂ7＋Ｃ27＋Ｄ80＝138。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,14 +736,14 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-31</t>
         </is>
       </c>
     </row>
@@ -754,14 +754,14 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-24</t>
         </is>
       </c>
     </row>
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
@@ -793,18 +793,18 @@
         <v>0</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>+29</t>
+          <t>+31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>※ Ａ23件の内訳は、ほかの照会にまとめたもの18件と、当方の作業又は村の決定で決着したもの5件です。まとめたものの代表例は、高齢者世帯等除雪サービス事業に関する6件（Ｍ-49・55・56・57・58・65）を実施要綱のご提供と障がいのある方が属する世帯の利用実績の1件（Ｍ-56）にまとめたことです。Ｂは、当方が置いた見込みの想定を村に尋ねていたもの（Ｍ-90）、受領済みの原典で決まるもの（Ｍ-43・Ｍ-44・Ｍ-101・Ｍ-116）、当方の編集上の事項（Ｓ-25）です。Ｃは、公表資料で書ける部分を当方が書き、固有の事実だけを尋ねる形に絞ったものです。</t>
+          <t>※ Ａ24件の内訳は、ほかの照会にまとめたもの19件と、当方の作業又は村の決定で決着したもの5件です。まとめたものの代表例は、高齢者世帯等除雪サービス事業に関する6件（Ｍ-49・55・56・57・58・65）を実施要綱のご提供と障がいのある方が属する世帯の利用実績の1件（Ｍ-56）にまとめたことです。Ｂは、当方が置いた見込みの想定を村に尋ねていたもの（Ｍ-90）、受領済みの原典で決まるもの（Ｍ-43・Ｍ-44・Ｍ-101・Ｍ-116）、当方の編集上の事項（Ｓ-25）です。Ｃは、公表資料で書ける部分を当方が書き、固有の事実だけを尋ねる形に絞ったものです。</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項133件の区分と判断の理由</t>
+          <t>確認事項138件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -887,9 +887,9 @@
           <t>Ｍ-13</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -899,10 +899,14 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人の支給決定の内容は村の支給決定の記録</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
+          <t>村の給付の台帳（令和8年10月22日受領）の利用先により、施設入所支援の4人はいずれも入所先の施設で生活介護をあわせて利用していると読めた。相違の有無はＭ-136に添えて伺う</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-136</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1025,9 +1029,9 @@
           <t>Ｍ-24</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>村外の事業所の一覧は村の支給決定の記録。これがないと事業所への照会文を作れない</t>
+          <t>村の給付の台帳（令和8年10月22日受領）により、サービス種別と事業所名が分かった。所在地は公表情報で当方が確かめる。事業所名は利用者が分かりうるため成果品には出さない</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
@@ -3409,7 +3413,7 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-136</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
@@ -3419,12 +3423,12 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>給付の台帳と協議会資料（資料２－３）の数え方</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>給付の台帳と協議会資料（資料２－３）の数え方（実施月の意味、計画相談支援の人数、排泄管理支援用具の令和7年度）は村の記録の作り方であり、当方では決められない。台帳で読めたＭ-13（施設入所と生活介護の同時の支給）をまとめ、相違の有無だけを添えて伺う</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr"/>
@@ -3432,7 +3436,7 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｍ-137</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -3442,12 +3446,12 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>台帳のご提供がなかったサービスの令和８年度の実績</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>台帳の提供がなかったサービスの令和8年度の実績は村の給付の記録</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr"/>
@@ -3455,7 +3459,7 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｍ-138</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
@@ -3465,12 +3469,12 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>成年後見制度利用支援事業の実績の食い違い</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>成年後見制度利用支援事業の実績が村の資料どうしで食い違う（資料２－３は0人、表6-3は2人・3人）。どちらが正しいかは村の記録</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr"/>
@@ -3478,49 +3482,45 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｍ-139</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>実績が見込量と離れているサービスの見込量の置き直し</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>見込量の置き直しは村の判断。当方は実績との離れをお示しするにとどめる</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-11</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr"/>
@@ -3574,45 +3574,49 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-20</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr"/>
@@ -3620,22 +3624,22 @@
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-22</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
@@ -3643,22 +3647,22 @@
     <row r="123" ht="36" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
-        </is>
-      </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-23</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr"/>
@@ -3666,7 +3670,7 @@
     <row r="124" ht="36" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -3676,12 +3680,12 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr"/>
@@ -3689,22 +3693,22 @@
     <row r="125" ht="36" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
-        </is>
-      </c>
-      <c r="B125" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr"/>
@@ -3712,22 +3716,22 @@
     <row r="126" ht="36" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｓ-26</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
@@ -3735,7 +3739,7 @@
     <row r="127" ht="36" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
+          <t>Ｓ-27</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -3745,39 +3749,35 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr"/>
     </row>
     <row r="128" ht="36" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-28</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
     <row r="129" ht="36" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
+          <t>Ｓ-29</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr"/>
@@ -3808,22 +3808,22 @@
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
-        </is>
-      </c>
-      <c r="B130" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
@@ -3831,45 +3831,49 @@
     <row r="131" ht="36" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-31</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-35</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
-        </is>
-      </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr"/>
     </row>
     <row r="132" ht="36" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
-        </is>
-      </c>
-      <c r="B132" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>計画の体系（章立て）と成果品の構え</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr"/>
@@ -3877,7 +3881,7 @@
     <row r="133" ht="36" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
@@ -3887,12 +3891,12 @@
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr"/>
@@ -3900,7 +3904,7 @@
     <row r="134" ht="36" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -3910,12 +3914,12 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
@@ -3923,7 +3927,7 @@
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -3933,12 +3937,12 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr"/>
@@ -3946,7 +3950,7 @@
     <row r="136" ht="36" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -3956,12 +3960,12 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr"/>
@@ -3969,7 +3973,7 @@
     <row r="137" ht="36" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -3979,12 +3983,12 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr"/>
@@ -3992,25 +3996,140 @@
     <row r="138" ht="36" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t>Ｓ-38</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-39</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr"/>
+    </row>
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="36" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr"/>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-42</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
         </is>
       </c>
-      <c r="E138" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-43</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>第５章の実績の表の書き換え（村の資料による）</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4027,7 +4146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4040,7 +4159,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの104件（村85件・他メンバー等19件）</t>
+          <t>ＣとＤの107件（村87件・他メンバー等20件）</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4200,7 @@
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-13</t>
+          <t>Ｍ-14</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -4091,7 +4210,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人の支給決定の内容</t>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -4101,14 +4220,14 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>施設入所支援4人の支給決定の内容は村の支給決定の記録</t>
+          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-14</t>
+          <t>Ｍ-15</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -4118,7 +4237,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数</t>
+          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -4128,14 +4247,14 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>介護保険の第2号被保険者で受給者証をお持ちの方の人数は村の台帳</t>
+          <t>令和9〜11年度に65歳に達する利用者の一覧は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-15</t>
+          <t>Ｍ-20</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -4145,7 +4264,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>令和9〜11年度に65歳に達する障がい福祉サービス利用者</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -4155,14 +4274,14 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>令和9〜11年度に65歳に達する利用者の一覧は村の台帳</t>
+          <t>令和9〜11年度に18歳・40歳に到達する利用者の一覧は村の台帳</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-20</t>
+          <t>Ｍ-21</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -4172,7 +4291,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>令和9〜11年度に18歳・40歳に到達する利用者</t>
+          <t>令和9〜11年度の特別支援学校・特別支援学級の卒業予定者</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -4182,14 +4301,14 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>令和9〜11年度に18歳・40歳に到達する利用者の一覧は村の台帳</t>
+          <t>卒業予定の方の一覧は教育委員会の記録。当方では把握できない</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-21</t>
+          <t>Ｍ-22</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -4199,7 +4318,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>令和9〜11年度の特別支援学校・特別支援学級の卒業予定者</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -4209,14 +4328,14 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>卒業予定の方の一覧は教育委員会の記録。当方では把握できない</t>
+          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数は村の把握</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-22</t>
+          <t>Ｍ-25</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -4226,7 +4345,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -4236,14 +4355,14 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>強度行動障害・高次脳機能障害・重症心身障害の方の人数は村の把握</t>
+          <t>事業所の職員の欠員・離職と休廃止の意向は村が事業所から聞き取るもの</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-24</t>
+          <t>Ｍ-26</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -4253,7 +4372,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>本村の住民が利用している村外の事業所の一覧</t>
+          <t>医療的ケア者（成人）と重症心身障害の状態にある成人の方</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -4263,14 +4382,14 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>村外の事業所の一覧は村の支給決定の記録。これがないと事業所への照会文を作れない</t>
+          <t>医療的ケア者（成人）と重症心身障害の成人の方の人数は村の把握</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-25</t>
+          <t>Ｍ-32</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -4280,7 +4399,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>事業所の職員の欠員・離職と休廃止の意向</t>
+          <t>手帳を所持していないが対象疾病に該当する方の人数</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -4290,14 +4409,14 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>事業所の職員の欠員・離職と休廃止の意向は村が事業所から聞き取るもの</t>
+          <t>手帳を所持していないが対象疾病に該当する方の人数は村の支給決定の記録</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-26</t>
+          <t>Ｍ-37</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -4307,24 +4426,24 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア者（成人）と重症心身障害の状態にある成人の方</t>
+          <t>給付費の財源構成（交付額と村の一般財源負担額）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア者（成人）と重症心身障害の成人の方の人数は村の把握</t>
+          <t>給付費の交付額と村の一般財源負担額は村の決算</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-32</t>
+          <t>Ｍ-42</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -4334,78 +4453,78 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>手帳を所持していないが対象疾病に該当する方の人数</t>
+          <t>個別避難計画の令和7年度の現在値</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>手帳を所持していないが対象疾病に該当する方の人数は村の支給決定の記録</t>
+          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-37</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-45</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>給付費の財源構成（交付額と村の一般財源負担額）</t>
+          <t>北塩原村地域公共交通計画</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>給付費の交付額と村の一般財源負担額は村の決算</t>
+          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-42</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-46</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の令和7年度の現在値</t>
+          <t>移動支援の対象事業所</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値が村の評価シート（1件）と協議会の回答（実質0件）で食い違う。村の内部データ</t>
+          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-45</t>
+          <t>Ｍ-47</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -4415,7 +4534,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画</t>
+          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -4425,24 +4544,24 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>北塩原村地域公共交通計画は公表物。計画のご提供を受け、障がいのある方の移動に関する記載の有無は当方で読む。ＩＣカード事業の利用実績のみ照会</t>
+          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-46</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-48</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>移動支援の対象事業所</t>
+          <t>村単独事業の実績</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -4452,24 +4571,24 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>県の指定事業所一覧が公表部分。移動支援を実施している事業所の特定は当方で行い、村の把握の状況のみ照会</t>
+          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-47</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-51</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>放課後等デイサービスの医療的ケア児の受入れ</t>
+          <t>権利擁護・成年後見の件数</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -4479,14 +4598,14 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>圏域の放課後等デイサービス事業所の一覧は公表部分。医療的ケア児の受入れの可否は事業所への照会が必要</t>
+          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-48</t>
+          <t>Ｍ-52</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
@@ -4496,7 +4615,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>村単独事業の実績</t>
+          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -4506,14 +4625,14 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>村単独事業4件の支給決定者数・事業費。村の決算データ。Ｍ-64（人工透析通院交通費助成）を含める</t>
+          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-51</t>
+          <t>Ｍ-53</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
@@ -4523,24 +4642,24 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の件数</t>
+          <t>就労の受け皿（職親委託等）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>権利擁護・成年後見の相談件数等6項目。村の相談記録</t>
+          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-52</t>
+          <t>Ｍ-54</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -4550,61 +4669,61 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布対象と障がい分野での活用</t>
+          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>緊急連絡カードの配布実績・実施課・消防との取決め。様式は受領済みだが運用は村の内部</t>
+          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-53</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-56</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>就労の受け皿（職親委託等）</t>
+          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>職親委託制度の実績・村内事業所の雇用実績・特別支援学校卒業者の就労先。村の把握</t>
+          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-54</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-60</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>地域生活支援拠点等の5機能の令和6・7年度の実績</t>
+          <t>手話出前講座の実績</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -4614,51 +4733,51 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>会津北部地域生活支援拠点の5機能ごとの実績と検証・検討の実施回数。Ｍ-86（代替調整の実績）を含める</t>
+          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-56</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-62</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>高齢者世帯等除雪サービス事業の助成の内容</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和8年10月27日</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>除雪に関する6件の受け皿。高齢者サービスの手引きは受領済みで、対象と助成の骨格は手引きで分かる。不足するのは実施要綱（「等」に障がいのみを理由とする世帯が入るか）と障がいのある方が属する世帯の利用実績のみ</t>
+          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-60</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-63</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>手話出前講座の実績</t>
+          <t>「つなぐ窓口」の相談実績</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -4668,41 +4787,41 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>手話言語条例（令和7年4月）は公表物。条例に基づく取組の実績（動画・出前講座）のみ照会。Ｍ-59 を含める</t>
+          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-62</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-68</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マーク・ほじょ犬マークの配布実績</t>
+          <t>物品等の調達方針と令和6年度以降の実績</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>ヘルプマーク・ヘルプカード・耳マーク・電話お願い手帳・おもいやり駐車場の配布実績。村の配布記録。Ｍ-61・Ｍ-73 を含める</t>
+          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-63</t>
+          <t>Ｍ-69</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
@@ -4712,24 +4831,24 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績</t>
+          <t>印刷の色</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月27日</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>「つなぐ窓口」の相談実績。村の相談記録</t>
+          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-68</t>
+          <t>Ｍ-70</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -4739,7 +4858,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>物品等の調達方針と令和6年度以降の実績</t>
+          <t>こども計画の名称と根拠法令</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -4749,14 +4868,14 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>障害者優先調達推進法第9条により調達方針と実績は公表が義務づけられている。方針のご提供を受け、内容は当方で読む</t>
+          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-69</t>
+          <t>Ｍ-71</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
@@ -4766,7 +4885,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>印刷の色</t>
+          <t>高齢者福祉事業の障がい者の利用</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -4776,14 +4895,14 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>印刷の色（カラーかモノクロか）。村の判断と費用</t>
+          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
         </is>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-70</t>
+          <t>Ｍ-72</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
@@ -4793,7 +4912,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>こども計画の名称と根拠法令</t>
+          <t>高齢者向けの共同生活の住まい</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -4803,14 +4922,14 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>計画名は村ホームページの記載が公表部分。根拠法令（こども基本法第10条第2項か子ども・子育て支援法第61条か）の判定は当方で行う。名称の確定のみ照会</t>
+          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-71</t>
+          <t>Ｍ-74</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
@@ -4820,7 +4939,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の障がい者の利用</t>
+          <t>子育て短期支援事業の障がい児の受入れ</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -4830,24 +4949,24 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>高齢者福祉事業の実施要綱における対象者の定めと、障がいのある方の利用実績。要綱は村の内部文書。Ｍ-50 を含める</t>
+          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-72</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-75</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>高齢者向けの共同生活の住まい</t>
+          <t>一般の子育て施策における障がい児の受入れ</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -4857,14 +4976,14 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システムで指定の有無は公表されている。知的障がい・精神障がいのある方の入居実績のみ照会</t>
+          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
         </is>
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-74</t>
+          <t>Ｍ-76</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
@@ -4874,7 +4993,7 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の障がい児の受入れ</t>
+          <t>早期発見から支援への接続件数</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4884,14 +5003,14 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>子育て短期支援事業の要件・委託先・受入れ可否の判断・令和8年度の利用実績。村の内部</t>
+          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
         </is>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-75</t>
+          <t>Ｍ-77</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -4901,7 +5020,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>一般の子育て施策における障がい児の受入れ</t>
+          <t>特別児童扶養手当の受給児童数</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -4911,24 +5030,24 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>一時預かり・こども誰でも通園制度・児童クラブにおける障がいのある子どもの受入れ体制と実績。村の内部</t>
+          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
         </is>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-76</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-78</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>早期発見から支援への接続件数</t>
+          <t>「わたしの思いノート」の配布と活用</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4938,24 +5057,24 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>新生児聴覚検査・乳幼児健診から支援につながった件数。村の母子保健の記録</t>
+          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
         </is>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-77</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-79</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数</t>
+          <t>人権相談の実績と受付の経路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -4965,14 +5084,14 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>特別児童扶養手当の受給児童数と通所支援の利用児童数。村の給付データ</t>
+          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-78</t>
+          <t>Ｍ-80</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
@@ -4982,7 +5101,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」の配布と活用</t>
+          <t>矯正施設を退所した方への支援の実績</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4992,24 +5111,24 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>「わたしの思いノート」は県が作成した様式で公表物。村での配布の有無と配布数のみ照会</t>
+          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
         </is>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-79</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-81</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>人権相談の実績と受付の経路</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -5019,14 +5138,14 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>みんなの人権110番・特設人権相談の仕組みは公表部分。村での受付の経路と件数のみ照会</t>
+          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-80</t>
+          <t>Ｍ-82</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
@@ -5036,7 +5155,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>矯正施設を退所した方への支援の実績</t>
+          <t>救急電話相談の代替手段</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -5046,14 +5165,14 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>福島県地域生活定着支援センターと保護観察所の役割は公表部分。村の相談実績と「社会を明るくする運動」推進委員会の構成のみ照会</t>
+          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-81</t>
+          <t>Ｍ-83</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
@@ -5063,7 +5182,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎ</t>
+          <t>個別避難計画の対象者への情報伝達</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -5073,14 +5192,14 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>65歳到達時の地域包括支援センターへの引継ぎの手順と件数。村の内部</t>
+          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-82</t>
+          <t>Ｍ-84</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
@@ -5090,7 +5209,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>救急電話相談の代替手段</t>
+          <t>AEDの設置状況と救命講習</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -5100,14 +5219,14 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>#7119・#8000の仕組みは公表部分。聴覚・言語障がいのある方の代替手段の有無のみ県へ照会</t>
+          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
         </is>
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-83</t>
+          <t>Ｍ-85</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
@@ -5117,7 +5236,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達</t>
+          <t>積雪・通行規制によるサービスの中断実績</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -5127,24 +5246,24 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>個別避難計画の対象者への情報伝達の手段と戸別受信機の配布。村の内部</t>
+          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-84</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-87</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>AEDの設置状況と救命講習</t>
+          <t>訪問系サービスの対象となりうる方の個別の状況</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -5154,24 +5273,24 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>ＡＥＤの設置場所は村ホームページ等で公表されている。夜間・休日に使えるカ所数と救命講習の実績のみ照会</t>
+          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-85</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-88</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績</t>
+          <t>訪問系サービスの有資格者の確保</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -5181,14 +5300,14 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>積雪・通行規制によるサービスの中断実績。村の記録（記録がない場合はその旨）</t>
+          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-87</t>
+          <t>Ｍ-89</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
@@ -5198,7 +5317,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>訪問系サービスの対象となりうる方の個別の状況</t>
+          <t>居宅介護の支給決定量と実利用量の差</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -5208,24 +5327,24 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>障害支援区分4以上・行動関連項目10点以上等の人数と意向確認の有無。村の台帳</t>
+          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-88</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-91</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>訪問系サービスの有資格者の確保</t>
+          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -5235,24 +5354,24 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>事業所の一覧は公表部分。訪問系は有資格者の有無で決まるため、有資格者数は事業所への照会が必要</t>
+          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-89</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-92</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差</t>
+          <t>就労系サービスの個人の経路</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -5262,14 +5381,14 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>居宅介護の支給決定量と実利用量の差とその理由。村の支給決定データ</t>
+          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-91</t>
+          <t>Ｍ-93</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
@@ -5279,7 +5398,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>医療的ケアを要する方のレスパイトと緊急時の受入れ</t>
+          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -5289,24 +5408,24 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児1人とその家族のレスパイトの意向、緊急時の受入れ先、18歳到達後の受入れ先。村の把握</t>
+          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
         </is>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-92</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-94</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>就労系サービスの個人の経路</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -5316,14 +5435,14 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>就労系サービスの見込みは当方が置いたものであり、想定は当方が明示する。村にお尋ねするのはその想定に当たる方が実在するかのみに絞る</t>
+          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-93</t>
+          <t>Ｍ-95</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
@@ -5333,7 +5452,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>精神科長期入院者の退院後の住まいと共同生活援助の内訳</t>
+          <t>第4次障がい者計画の指標の最新値</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -5343,14 +5462,14 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>長期入院の方1人の退院の年度・住まい・日中活動と、共同生活援助の増加1人が誰かの特定。村の把握</t>
+          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
         </is>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-94</t>
+          <t>Ｍ-96</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
@@ -5360,7 +5479,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向</t>
+          <t>障がいのある方の特定健康診査の受診状況</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -5370,14 +5489,14 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援4人それぞれの地域生活への移行の意向。本人・家族の意向であり村を通じた個別の確認が必要</t>
+          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-95</t>
+          <t>Ｍ-97</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
@@ -5387,24 +5506,24 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の指標の最新値</t>
+          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>第4次計画の8指標のうち5指標の令和7年度実績。村の内部データ</t>
+          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-96</t>
+          <t>Ｍ-98</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
@@ -5414,24 +5533,24 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況</t>
+          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>障がいのある方の特定健康診査の受診状況。村のＫＤＢデータ</t>
+          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-97</t>
+          <t>Ｍ-99</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
@@ -5441,24 +5560,24 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と令和９〜11年度に年５人を見込む根拠</t>
+          <t>福島県（会津保健福祉事務所）への照会</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度利用支援事業の実施要綱と年5人の見込みの根拠。要綱は村の内部文書</t>
+          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-98</t>
+          <t>Ｍ-100</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
@@ -5468,7 +5587,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>会津北部４町村共同確認票による猪苗代町・磐梯町・湯川村への照会</t>
+          <t>医療的ケア児等コーディネーターとして数えている方</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -5478,24 +5597,24 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>会津北部4町村（猪苗代町・磐梯町・湯川村）への照会。村を通じてお願いする</t>
+          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-99</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-102</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会</t>
+          <t>児童発達支援センターの４つの中核機能の接続先</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -5505,14 +5624,14 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>福島県（会津保健福祉事務所）への照会。村を通じてお願いする</t>
+          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
         </is>
       </c>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-100</t>
+          <t>Ｍ-103</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr">
@@ -5522,24 +5641,24 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>医療的ケア児等コーディネーターとして数えている方の特定。村の内部</t>
+          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-102</t>
+          <t>Ｍ-104</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -5549,34 +5668,34 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>児童発達支援センターの４つの中核機能の接続先</t>
+          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>会津若松市の児童発達支援センターは公表部分で特定できる。本村の児童への対応の可否のみ照会</t>
+          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
         </is>
       </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-103</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-105</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無</t>
+          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -5586,14 +5705,14 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>村が運営する障害福祉サービス等の事業所の有無。村のみが答えられる（1行で足りる）</t>
+          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
         </is>
       </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-104</t>
+          <t>Ｍ-106</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -5603,24 +5722,24 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>村内の対象事業所の情報公表の状況（令和７年度の実績）</t>
+          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>障害福祉サービス等情報公表システムは公表物であるが当方の環境から接続できない。村内の対象事業所の公表状況のご提供をお願いし、公表率・更新率の算定は当方で行う</t>
+          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-105</t>
+          <t>Ｍ-107</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -5630,34 +5749,34 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
+          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>家庭・教育・福祉の連携を進める国の事業と地域連携推進マネジャーの仕組みは公表部分。本村での実施の有無のみ照会</t>
+          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
         </is>
       </c>
     </row>
     <row r="64" ht="34" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-106</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-108</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>村内の事業所の指定の形と、障がいのある方の受入れの状況</t>
+          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5667,41 +5786,41 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>村内の介護保険事業所の指定の形は介護サービス情報公表システムで公表されている。障がいのある方の受入れの状況のみ照会</t>
+          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
         </is>
       </c>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-107</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-109</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う県の体制と村の対応</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和8年10月20日</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>高次脳機能障害者支援法の施行に伴う留意事項について（障精発0415第1号）を受領済みで、法の内容は当方で整理した。県の体制のみ県へ照会</t>
+          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
         </is>
       </c>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-108</t>
+          <t>Ｍ-110</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
@@ -5711,51 +5830,51 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と、その要綱における対象者の定め</t>
+          <t>障害者基本法第36条の合議制の機関の有無</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>本村が実施している地域支援事業と要綱における対象者の定め。要綱は村の内部文書</t>
+          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
         </is>
       </c>
     </row>
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-109</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-111</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方</t>
+          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月20日</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>施設入所支援の利用者のうち継続入所者に当たる方。村の台帳</t>
+          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
         </is>
       </c>
     </row>
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-110</t>
+          <t>Ｍ-112</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
@@ -5765,51 +5884,51 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無</t>
+          <t>成果品の印刷・製本の所要日数と発注の形</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>障害者基本法第36条の合議制の機関の有無。村のみが答えられる（1行で足りる）</t>
+          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
         </is>
       </c>
     </row>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-111</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-113</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>生涯学習・スポーツ・文化の事業の一覧は村ホームページにあるものが公表部分。障がいのある方の参加実績のみ照会。Ｍ-66（パラスポーツ）を含める</t>
+          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
         </is>
       </c>
     </row>
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-112</t>
+          <t>Ｍ-114</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
@@ -5819,51 +5938,51 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>成果品の印刷・製本の所要日数と発注の形</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>印刷・製本の発注の形（村か業者か）と所要日数。部数・折り方を含め村の判断</t>
+          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
         </is>
       </c>
     </row>
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-113</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-115</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数（村の手帳台帳）</t>
+          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の令和6・7・8年の実数。村の手帳台帳</t>
+          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
         </is>
       </c>
     </row>
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-114</t>
+          <t>Ｍ-117</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
@@ -5873,24 +5992,24 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針</t>
+          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年12月12日（金）</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度法人後見支援事業の年度ごとの方針。村の方針</t>
+          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
         </is>
       </c>
     </row>
     <row r="73" ht="34" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-115</t>
+          <t>Ｍ-118</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
@@ -5900,7 +6019,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>計画相談支援のモニタリングの負荷と、期首の必要者数・22歳到達</t>
+          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -5910,14 +6029,14 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの負荷の計算は当方で行う。村にお尋ねするのは期首の必要者数と22歳到達の人数のみに絞る</t>
+          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
         </is>
       </c>
     </row>
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-117</t>
+          <t>Ｍ-119</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
@@ -5927,159 +6046,159 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターと会津権利擁護・成年後見センターの関係</t>
+          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>令和８年12月12日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>地域権利擁護相談支援センターとしての位置付けを11市町村でどのように協議するか。村と関係市町村の協議</t>
+          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-118</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-120</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>サービス量の中長期的な推計を本計画に載せるかどうか</t>
+          <t>医療的ケアの担い手と非常用電源</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法（令和8年法律第51号）の概要は受領済みで、中長期推計の求めの内容は当方で整理した。当方が案を示し、本計画に載せるかの採否のみ村に伺う</t>
+          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
         </is>
       </c>
     </row>
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-119</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-121</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>避難の名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納</t>
+          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>避難行動要支援者名簿と訓練、精神科病院の入院先と退院に至らなかった理由、介護保険料の未納。村の内部</t>
+          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
         </is>
       </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-120</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-122</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>医療的ケアの担い手と非常用電源</t>
+          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>喀痰吸引等の認定を受けた方と登録特定行為事業者、非常用電源。村の把握</t>
+          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
         </is>
       </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-121</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-124</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>村内の事業主の規模と村役場の障がい者雇用、農福連携</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>障害者雇用状況報告は公表部分。村役場の障がい者雇用率と農福連携の状況のみ照会</t>
+          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-122</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-125</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画（第2期）と医療的ケア児の住まい</t>
+          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>障がい者活躍推進計画は障害者雇用促進法第7条の3により公表が義務づけられている。計画のご提供を受け、内容は当方で読む。Ｍ-67 を含める</t>
+          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-124</t>
+          <t>Ｍ-126</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -6089,24 +6208,24 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所</t>
+          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>策定委員会資料の令和6年・令和7年の手帳所持者数の出所。村の資料の作成経緯</t>
+          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-125</t>
+          <t>Ｍ-127</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -6116,51 +6235,51 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>計画策定の工程の引き直し（パブリックコメント・庁議・議会）</t>
+          <t>障がい児支援の人材と事業所の継続</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>案Ａの3点（パブリックコメントの1月下旬開始・庁議2月19日・議会を決定の後に置くこと）の了解と、4つの開催日。村の意思決定であり当方では決められない。Ｍ-40・Ｍ-123 を含める</t>
+          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-126</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｍ-129</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会と本村の協議の場</t>
+          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年10月24日（金）</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>医療的ケア児等支援地域協議会への参画と村の協議の場の役割分担。村の判断。Ｍ-41 を含める</t>
+          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-127</t>
+          <t>Ｍ-130</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -6170,51 +6289,51 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続</t>
+          <t>村内へのグループホームの設置の検討</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>障がい児支援の人材と事業所の継続の見通し。村の把握</t>
+          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
         </is>
       </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-129</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｍ-131</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画の欠けている章と村内の医療資源</t>
+          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月24日（金）</t>
+          <t>令和８年11月28日（金）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>第8次福島県医療計画は公表物であり、手元に無い第3章・第10章のご提供をお願いする。村内の医療資源（診療所の診療日・薬局・消防本部）は村にお尋ねする</t>
+          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
         </is>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-130</t>
+          <t>Ｍ-132</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
@@ -6224,7 +6343,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置の検討</t>
+          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -6234,14 +6353,14 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>村内へのグループホームの設置を検討するかは村の政策判断。当方で置けない</t>
+          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
         </is>
       </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-131</t>
+          <t>Ｍ-133</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
@@ -6251,24 +6370,24 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の登録勧奨の実績と電話以外の相談の手段</t>
+          <t>北塩原村障がい者自立支援協議会の委員名簿（令和8年度時点）</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月28日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>ＮＥＴ１１９の本村の登録者数と登録勧奨の実績は村の内部の記録。制度そのものは前期計画で確認済み</t>
+          <t>自立支援協議会の令和8年度時点の委員は村の委嘱の記録。資料編に実名が載るため当方の推測では置けない</t>
         </is>
       </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-132</t>
+          <t>Ｍ-134</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -6278,7 +6397,7 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>アンケート調査結果報告書の自由記述の要約の程度</t>
+          <t>障がい者相談支援事業の2カ所のうち村の担当課</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -6288,14 +6407,14 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>自由記述をどこまで要約するかは公表の判断であり村の決定。当方は要約案をお示しするにとどめる</t>
+          <t>相談支援事業を担う課の名称と改編の経緯は村の内部。村ホームページでは保健福祉課が相談の窓口であることまでしか分からない</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-133</t>
+          <t>Ｍ-135</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -6305,7 +6424,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>北塩原村障がい者自立支援協議会の委員名簿（令和8年度時点）</t>
+          <t>北塩原村の地域福祉計画の有無と策定の状況</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -6315,14 +6434,14 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会の令和8年度時点の委員は村の委嘱の記録。資料編に実名が載るため当方の推測では置けない</t>
+          <t>地域福祉計画の有無と策定の予定は村の判断。村ホームページは当方の環境から閲覧できない</t>
         </is>
       </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>Ｍ-134</t>
+          <t>Ｍ-136</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
@@ -6332,7 +6451,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>障がい者相談支援事業の2カ所のうち村の担当課</t>
+          <t>給付の台帳と協議会資料（資料２－３）の数え方</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -6342,14 +6461,14 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>相談支援事業を担う課の名称と改編の経緯は村の内部。村ホームページでは保健福祉課が相談の窓口であることまでしか分からない</t>
+          <t>給付の台帳と協議会資料（資料２－３）の数え方（実施月の意味、計画相談支援の人数、排泄管理支援用具の令和7年度）は村の記録の作り方であり、当方では決められない。台帳で読めたＭ-13（施設入所と生活介護の同時の支給）をまとめ、相違の有無だけを添えて伺う</t>
         </is>
       </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-135</t>
+          <t>Ｍ-137</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
@@ -6359,7 +6478,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>北塩原村の地域福祉計画の有無と策定の状況</t>
+          <t>台帳のご提供がなかったサービスの令和８年度の実績</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -6369,14 +6488,14 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>地域福祉計画の有無と策定の予定は村の判断。村ホームページは当方の環境から閲覧できない</t>
+          <t>台帳の提供がなかったサービスの令和8年度の実績は村の給付の記録</t>
         </is>
       </c>
     </row>
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-138</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
@@ -6386,7 +6505,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>成年後見制度利用支援事業の実績の食い違い</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -6396,14 +6515,14 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>成年後見制度利用支援事業の実績が村の資料どうしで食い違う（資料２－３は0人、表6-3は2人・3人）。どちらが正しいかは村の記録</t>
         </is>
       </c>
     </row>
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｍ-139</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -6413,24 +6532,24 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>実績が見込量と離れているサービスの見込量の置き直し</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>見込量の置き直しは村の判断。当方は実績との離れをお示しするにとどめる</t>
         </is>
       </c>
     </row>
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
@@ -6440,24 +6559,24 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -6467,24 +6586,24 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
@@ -6494,7 +6613,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6504,14 +6623,14 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="96" ht="34" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -6521,7 +6640,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -6531,14 +6650,14 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="97" ht="34" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
@@ -6548,24 +6667,24 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -6575,51 +6694,51 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="99" ht="34" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B99" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｓ-28</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
+          <t>Ｓ-29</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -6629,51 +6748,51 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
-        </is>
-      </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月16日（金）</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -6683,24 +6802,24 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
     </row>
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
@@ -6710,7 +6829,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6720,14 +6839,14 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -6737,24 +6856,24 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
     </row>
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
@@ -6764,24 +6883,24 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6791,24 +6910,24 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
@@ -6818,7 +6937,7 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -6828,14 +6947,14 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6845,44 +6964,125 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-40</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="34" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-41</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="34" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-42</t>
         </is>
       </c>
-      <c r="B109" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="B111" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
         <is>
           <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr">
+      <c r="E111" s="9" t="inlineStr">
         <is>
           <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="34" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-43</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>第５章の実績の表の書き換え（村の資料による）</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
         </is>
       </c>
     </row>
@@ -6901,7 +7101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6913,7 +7113,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ほかの照会にまとめた18件（12件に集約）</t>
+          <t>ほかの照会にまとめた19件（13件に集約）</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7349,12 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
+          <t>Ｍ-136</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>給付の台帳と協議会資料（資料２－３）の数え方</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -7162,25 +7362,45 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Ｓ-20（緑と青の組合せ）</t>
+          <t>Ｍ-13（施設入所支援4人の支給決定の内容）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-30</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Ｓ-20（緑と青の組合せ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>基本指針の追加告示の入手と最終照合</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Ｓ-31（基本指針の令和8年10月の追加改正の出所）</t>
         </is>

--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ24＋Ｂ7＋Ｃ27＋Ｄ80＝138。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ24＋Ｂ7＋Ｃ27＋Ｄ81＝139。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項138件の区分と判断の理由</t>
+          <t>確認事項139件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-140</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>就労定着支援事業の利用者数の基準値と目標値</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>就労定着支援の基準値は０人に改めたが、目標値（２人）を据え置くかは村の判断。令和８年度の利用者が一般就労への移行者であるかは村の支給決定の記録</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr"/>
@@ -3574,34 +3574,30 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-19</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr"/>
     </row>
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
+          <t>Ｓ-20</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -3611,35 +3607,39 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
-        </is>
-      </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
     <row r="123" ht="36" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr"/>
@@ -3670,7 +3670,7 @@
     <row r="124" ht="36" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr"/>
@@ -3693,22 +3693,22 @@
     <row r="125" ht="36" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｓ-24</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr"/>
@@ -3716,22 +3716,22 @@
     <row r="126" ht="36" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
@@ -3739,7 +3739,7 @@
     <row r="127" ht="36" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
+          <t>Ｓ-26</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr"/>
@@ -3762,22 +3762,22 @@
     <row r="128" ht="36" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
-        </is>
-      </c>
-      <c r="B128" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-27</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
     <row r="129" ht="36" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr"/>
@@ -3808,22 +3808,22 @@
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
@@ -3831,34 +3831,30 @@
     <row r="131" ht="36" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr"/>
     </row>
     <row r="132" ht="36" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
+          <t>Ｓ-31</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -3868,35 +3864,39 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr"/>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="36" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B133" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>計画の体系（章立て）と成果品の構え</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
     <row r="134" ht="36" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
@@ -3927,7 +3927,7 @@
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
     <row r="136" ht="36" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
     <row r="137" ht="36" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
     <row r="138" ht="36" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
     <row r="139" ht="36" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
     <row r="140" ht="36" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
     <row r="141" ht="36" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-40</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-42</t>
+          <t>Ｓ-41</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr"/>
@@ -4111,25 +4111,48 @@
     <row r="143" ht="36" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr"/>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B143" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
         <is>
           <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr"/>
+      <c r="E144" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4146,7 +4169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4159,7 +4182,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの107件（村87件・他メンバー等20件）</t>
+          <t>ＣとＤの108件（村88件・他メンバー等20件）</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6572,7 @@
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-140</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
@@ -6559,7 +6582,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>就労定着支援事業の利用者数の基準値と目標値</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6569,14 +6592,14 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>就労定着支援の基準値は０人に改めたが、目標値（２人）を据え置くかは村の判断。令和８年度の利用者が一般就労への移行者であるかは村の支給決定の記録</t>
         </is>
       </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -6586,24 +6609,24 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
@@ -6613,24 +6636,24 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="34" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -6640,7 +6663,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -6650,14 +6673,14 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="97" ht="34" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
@@ -6667,7 +6690,7 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6677,14 +6700,14 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -6694,7 +6717,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -6704,14 +6727,14 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="99" ht="34" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
@@ -6721,24 +6744,24 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -6748,7 +6771,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -6758,68 +6781,68 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B102" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月16日（金）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
     </row>
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
@@ -6829,7 +6852,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6839,14 +6862,14 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -6856,24 +6879,24 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
     </row>
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
@@ -6883,24 +6906,24 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6910,7 +6933,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -6920,14 +6943,14 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
@@ -6937,24 +6960,24 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6964,24 +6987,24 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
@@ -6991,24 +7014,24 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-40</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -7018,7 +7041,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -7028,14 +7051,14 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
         </is>
       </c>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-42</t>
+          <t>Ｓ-41</t>
         </is>
       </c>
       <c r="B111" s="15" t="inlineStr">
@@ -7045,7 +7068,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -7055,32 +7078,59 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
     </row>
     <row r="112" ht="34" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="34" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B112" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
         </is>

--- a/output/北塩原村_確認事項の区分.xlsx
+++ b/output/北塩原村_確認事項の区分.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Ａ24＋Ｂ7＋Ｃ27＋Ｄ81＝139。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
+          <t>Ａ24＋Ｂ7＋Ｃ27＋Ｄ82＝140。Ｍ-40からＭ-129（90件）とＳ-12からＳ-38（21件）。欠番・重複がないことを生成のたびに検算している</t>
         </is>
       </c>
     </row>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項139件の区分と判断の理由</t>
+          <t>確認事項140件の区分と判断の理由</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
     <row r="118" ht="36" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-141</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>障がい児の台帳と協議会資料（資料２－３）の令和７年度の食い違い</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>障がい児の台帳と資料２－３の令和7年度の食い違い（児童発達支援・障がい児相談支援）は村の記録の作り方</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
@@ -3551,7 +3551,7 @@
     <row r="119" ht="36" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
     <row r="120" ht="36" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
@@ -3597,34 +3597,30 @@
     <row r="121" ht="36" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-20</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-19</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr"/>
     </row>
     <row r="122" ht="36" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-21</t>
+          <t>Ｓ-20</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -3634,35 +3630,39 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次</t>
+          <t>緑と青の組合せ</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr"/>
+          <t>緑と青の組合せ。当方で白黒に変換したときの明度差を検査し、25未満となる組合せが0件であることを生成のたびに確かめている。Ｓ-30 にまとめる</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="36" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-21</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図表番号と図表目次</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図表番号と図表目次。当方で図26点・表96点に番号と表題を付け、目次の後に図表目次を置いた。実施済み</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr"/>
@@ -3670,7 +3670,7 @@
     <row r="124" ht="36" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr"/>
@@ -3693,7 +3693,7 @@
     <row r="125" ht="36" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr"/>
@@ -3716,22 +3716,22 @@
     <row r="126" ht="36" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-25</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>Ｂ 当方で確認</t>
+          <t>Ｓ-24</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
@@ -3739,22 +3739,22 @@
     <row r="127" ht="36" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-26</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-25</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ 当方で確認</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目</t>
+          <t>制度名称の表記の統一</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
+          <t>制度名称の表記の統一。計画冒頭の注記が定めた規則（法律用語や施設名等の固有名称を除きひらがな）に従って当方の正本で統一する。当方で解消すべき編集上の事項</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr"/>
@@ -3762,7 +3762,7 @@
     <row r="128" ht="36" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-27</t>
+          <t>Ｓ-26</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制</t>
+          <t>優先してクロスする5項目</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
+          <t>優先してクロスする5項目。集計表の改訂版により課題が8件であることが確定し、新設された「集計_障がい別」シートで必要な集計が得られた。表2-8 に8区分目を足して決着（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
@@ -3785,22 +3785,22 @@
     <row r="129" ht="36" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
-        </is>
-      </c>
-      <c r="B129" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-27</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>第1章5（4）の時制。工程の引き直し（案Ａ）に伴い当方が書き換えた（ＴＫ-4）</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
     <row r="130" ht="36" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
@@ -3831,22 +3831,22 @@
     <row r="131" ht="36" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>Ｃ 公表資料で先行</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr"/>
@@ -3854,34 +3854,30 @@
     <row r="132" ht="36" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-31</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>Ａ 解決済み</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>Ｃ 公表資料で先行</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>Ｓ-35</t>
-        </is>
-      </c>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="36" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-32</t>
+          <t>Ｓ-31</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -3891,35 +3887,39 @@
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え</t>
+          <t>基本指針の令和8年10月の追加改正の出所</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
-        </is>
-      </c>
-      <c r="E133" s="8" t="inlineStr"/>
+          <t>基本指針の令和8年10月の追加改正の出所。Ｓ-35（追加告示の入手と最終照合）にまとめる</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>Ｓ-35</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="36" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
+          <t>Ｓ-32</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Ａ 解決済み</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>計画の体系（章立て）と成果品の構え</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>計画の体系（章立て）と成果品の構え。令和8年10月14日に村が案Ｃ（折衷）と案②を採用し決着</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
@@ -3927,7 +3927,7 @@
     <row r="135" ht="36" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
     <row r="136" ht="36" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
     <row r="137" ht="36" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
     <row r="138" ht="36" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr"/>
@@ -4019,7 +4019,7 @@
     <row r="139" ht="36" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
     <row r="140" ht="36" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
     <row r="141" ht="36" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr"/>
@@ -4088,7 +4088,7 @@
     <row r="142" ht="36" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-40</t>
         </is>
       </c>
       <c r="B142" s="11" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr"/>
@@ -4111,7 +4111,7 @@
     <row r="143" ht="36" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-42</t>
+          <t>Ｓ-41</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr"/>
@@ -4134,25 +4134,48 @@
     <row r="144" ht="36" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B144" s="11" t="inlineStr">
-        <is>
-          <t>Ｄ 相手の回答が必要</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>Ｄ 相手の回答が必要</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D145" s="9" t="inlineStr">
         <is>
           <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr"/>
+      <c r="E145" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4169,7 +4192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4182,7 +4205,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＣとＤの108件（村88件・他メンバー等20件）</t>
+          <t>ＣとＤの109件（村89件・他メンバー等20件）</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6622,7 @@
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-11</t>
+          <t>Ｍ-141</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -6609,7 +6632,7 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
+          <t>障がい児の台帳と協議会資料（資料２－３）の令和７年度の食い違い</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -6619,14 +6642,14 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
+          <t>障がい児の台帳と資料２－３の令和7年度の食い違い（児童発達支援・障がい児相談支援）は村の記録の作り方</t>
         </is>
       </c>
     </row>
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-12</t>
+          <t>Ｓ-11</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
@@ -6636,24 +6659,24 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
+          <t>特定地域サービス等の対象地域の基準、県が定める区域の指定の予定、障がい福祉分野での施行期日。あわせて法律番号・施行期日の原典</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月31日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
+          <t>特定地域サービス等の対象地域の基準と県が定める区域の指定の予定、障がい福祉分野での施行期日。法律の公布（令和8年6月）までは当方で確認済みであり、残るのは県が示す基準と時期。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="34" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-19</t>
+          <t>Ｓ-12</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -6663,24 +6686,24 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>図の元データ</t>
+          <t>意思決定支援ガイドライン（第２版）を用いた県研修の予定</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和8年10月31日</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
+          <t>意思決定支援ガイドライン第2版を用いた県研修の予定。県へのお取次ぎ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="34" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-22</t>
+          <t>Ｓ-19</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
@@ -6690,7 +6713,7 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>図２-８の表題</t>
+          <t>図の元データ</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6700,14 +6723,14 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
+          <t>図の元データ（Excel等）のご共有。他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-23</t>
+          <t>Ｓ-22</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -6717,7 +6740,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複</t>
+          <t>図２-８の表題</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -6727,14 +6750,14 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
+          <t>図2-8の表題の確認と画像の作り直し。原データは他メンバーの手元にある</t>
         </is>
       </c>
     </row>
     <row r="99" ht="34" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-24</t>
+          <t>Ｓ-23</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
@@ -6744,7 +6767,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>画像内の表題の扱い</t>
+          <t>計画の位置づけ図の重複</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6754,14 +6777,14 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
+          <t>計画の位置づけ図の重複の整理。図の作り直しが必要であり他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-28</t>
+          <t>Ｓ-24</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -6771,24 +6794,24 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典</t>
+          <t>画像内の表題の扱い</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
+          <t>画像内に焼き込まれた表題を外すこと。他メンバーの作業</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-29</t>
+          <t>Ｓ-28</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
@@ -6798,7 +6821,7 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
+          <t>モニタリングの標準の期間を定める告示の原典</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6808,68 +6831,68 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
+          <t>モニタリングの標準の期間を定める告示の原典。当方の環境からe-Gov等へ接続できないため入手を依頼</t>
         </is>
       </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-30</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
+          <t>Ｓ-29</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月16日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
+          <t>介護保険事業計画の中長期推計との年次の揃え方。高齢者側の担当との協議</t>
         </is>
       </c>
     </row>
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-33</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
+          <t>Ｓ-30</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更と目次の更新</t>
+          <t>ロービジョンへの配慮（文字の大きさ、模様、テキスト版）</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月16日（金）</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
+          <t>ロービジョンへの配慮。色の明度差は当方で検査済み（Ｓ-20を含める）。文字の大きさとテキスト版の取扱いのみ了解をいただく</t>
         </is>
       </c>
     </row>
     <row r="104" ht="34" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-34</t>
+          <t>Ｓ-33</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -6879,7 +6902,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
+          <t>第3章の章題の変更と目次の更新</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -6889,14 +6912,14 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
+          <t>第3章の章題の変更に伴うＷｏｒｄの目次の更新。当方の環境では目次フィールドを更新できない</t>
         </is>
       </c>
     </row>
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-35</t>
+          <t>Ｓ-34</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
@@ -6906,24 +6929,24 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにする</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
+          <t>概要版のグラフをモノクロ印刷で読めるようにすること。他メンバーの作図</t>
         </is>
       </c>
     </row>
     <row r="106" ht="34" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-36</t>
+          <t>Ｓ-35</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -6933,24 +6956,24 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
+          <t>基本指針の追加告示の入手と最終照合</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月16日</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
+          <t>基本指針の追加告示の入手と最終照合。当方の環境から厚生労働省等へ接続できない。Ｓ-31 を含める</t>
         </is>
       </c>
     </row>
     <row r="107" ht="34" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-37</t>
+          <t>Ｓ-36</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
@@ -6960,7 +6983,7 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -6970,14 +6993,14 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
+          <t>アンケート結果報告の概要版と分析報告書の確定値の照合。分析報告書の作成者の確認が必要</t>
         </is>
       </c>
     </row>
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-38</t>
+          <t>Ｓ-37</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -6987,24 +7010,24 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和8年10月16日</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
+          <t>集計表の改訂版の確認結果（基数1〜2の区分の注記と課題8件）。報告書の側の対応が必要</t>
         </is>
       </c>
     </row>
     <row r="109" ht="34" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-39</t>
+          <t>Ｓ-38</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
@@ -7014,24 +7037,24 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への差し替え（第2章7の割合）</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>令和８年11月14日（金）</t>
+          <t>令和８年10月31日（金）</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
+          <t>県医療計画と県障がい福祉計画の指標の食い違い。県へのお取次ぎを含む</t>
         </is>
       </c>
     </row>
     <row r="110" ht="34" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-40</t>
+          <t>Ｓ-39</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -7041,24 +7064,24 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>報告書 令和8年10月22日版の直し残し11か所</t>
+          <t>回収数40件への差し替え（第2章7の割合）</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>令和８年10月31日（金）</t>
+          <t>令和８年11月14日（金）</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
+          <t>回収数40件への第2章7の差し替え。他メンバーが作成された素案の本文であり、当方が本文を書き換えるのは事実として誤っているものに限るという取決めがある</t>
         </is>
       </c>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>Ｓ-41</t>
+          <t>Ｓ-40</t>
         </is>
       </c>
       <c r="B111" s="15" t="inlineStr">
@@ -7068,7 +7091,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
+          <t>報告書 令和8年10月22日版の直し残し11か所</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
@@ -7078,14 +7101,14 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
+          <t>報告書の直し残し11か所のお戻し。うち2か所（移動支援の語の選択、避難所の「安全性」と「支え合い」の趣旨）は意図の確認が要る</t>
         </is>
       </c>
     </row>
     <row r="112" ht="34" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Ｓ-42</t>
+          <t>Ｓ-41</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -7095,7 +7118,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+          <t>第6章 課題2 の「第二種運送事業者」「福祉運送事業等の事業者指定」</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -7105,32 +7128,59 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+          <t>「第二種運送事業者」「福祉運送事業等の事業者指定」がどの制度を指すか。道路運送法の原典を当方は持っておらず、外部のサイトも閲覧できない</t>
         </is>
       </c>
     </row>
     <row r="113" ht="34" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
+          <t>Ｓ-42</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘20件のうち手の付いていないものの扱い</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>令和８年10月31日（金）</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>当方のレビュー指摘のうちどこまでを報告書に入れるかは報告書を作成される他メンバーの判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
           <t>Ｓ-43</t>
         </is>
       </c>
-      <c r="B113" s="15" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>第５章の実績の表の書き換え（村の資料による）</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>令和８年10月31日（金）</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>実績の表の元の値に別の出所があるかは他メンバー版を作成された方にしか分からない</t>
         </is>
